--- a/data/positions/Posição Consolidada - 11370136.xlsx
+++ b/data/positions/Posição Consolidada - 11370136.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 11370136 | 21/08/2026, 14:50</x:t>
+    <x:t>Conta: 11370136 | 25/08/2026, 19:23</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>32,2%|Renda Fixa</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.534.994,83</x:t>
+    <x:t>R$ 1.536.346,29</x:t>
   </x:si>
   <x:si>
     <x:t>32,20%|Pós-Fixada</x:t>
@@ -94,10 +94,10 @@
     <x:t>R$ 1.222.011,09</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.223.631,07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.222.173,09</x:t>
+    <x:t>R$ 1.224.712,24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.222.659,36</x:t>
   </x:si>
   <x:si>
     <x:t>LCI CEF - NOV/2026</x:t>
@@ -115,16 +115,16 @@
     <x:t>R$ 310.958,77</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 311.363,76</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 310.999,27</x:t>
+    <x:t>R$ 311.634,05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 311.120,84</x:t>
   </x:si>
   <x:si>
     <x:t>58,0%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.761.381,15</x:t>
+    <x:t>R$ 2.763.806,78</x:t>
   </x:si>
   <x:si>
     <x:t>57,90%|Pós-Fixada</x:t>
@@ -145,10 +145,10 @@
     <x:t>R$ 1.258.510,52</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.260.722,48</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.260.224,79</x:t>
+    <x:t>R$ 1.261.829,91</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.261.083,05</x:t>
   </x:si>
   <x:si>
     <x:t>20/08/2026</x:t>
@@ -163,16 +163,16 @@
     <x:t>R$ 1.500.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.500.658,67</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.500.510,47</x:t>
+    <x:t>R$ 1.501.976,87</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.501.532,07</x:t>
   </x:si>
   <x:si>
     <x:t>9,81%|Fundos de Investimento</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 467.471,34</x:t>
+    <x:t>R$ 467.700,02</x:t>
   </x:si>
   <x:si>
     <x:t>9,80%|Fundos de Renda Fixa Pós-Fixado</x:t>
@@ -193,10 +193,10 @@
     <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
   </x:si>
   <x:si>
-    <x:t>21/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 272,02</x:t>
+    <x:t>24/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 272,16</x:t>
   </x:si>
   <x:si>
     <x:t>1.718,50</x:t>
@@ -205,7 +205,7 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 467.025,57</x:t>
+    <x:t>R$ 467.092,23</x:t>
   </x:si>
   <x:si>
     <x:t>0,01%|Saldo projetado</x:t>
@@ -849,10 +849,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>4764364.71377368</x:v>
+        <x:v>4768370.49526831</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>4763847.31377368</x:v>
+        <x:v>4767853.09526831</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>517.4</x:v>

--- a/data/positions/Posição Consolidada - 11370136.xlsx
+++ b/data/positions/Posição Consolidada - 11370136.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 11370136 | 25/08/2026, 19:23</x:t>
+    <x:t>Conta: 11370136 | 28/08/2026, 09:34</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>32,2%|Renda Fixa</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.536.346,29</x:t>
+    <x:t>R$ 1.538.375,72</x:t>
   </x:si>
   <x:si>
     <x:t>32,20%|Pós-Fixada</x:t>
@@ -94,10 +94,10 @@
     <x:t>R$ 1.222.011,09</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.224.712,24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.222.659,36</x:t>
+    <x:t>R$ 1.226.335,80</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.223.481,49</x:t>
   </x:si>
   <x:si>
     <x:t>LCI CEF - NOV/2026</x:t>
@@ -115,16 +115,16 @@
     <x:t>R$ 310.958,77</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 311.634,05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 311.120,84</x:t>
+    <x:t>R$ 312.039,92</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 311.326,36</x:t>
   </x:si>
   <x:si>
     <x:t>58,0%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.763.806,78</x:t>
+    <x:t>R$ 2.767.449,23</x:t>
   </x:si>
   <x:si>
     <x:t>57,90%|Pós-Fixada</x:t>
@@ -145,10 +145,10 @@
     <x:t>R$ 1.258.510,52</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.261.829,91</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.261.083,05</x:t>
+    <x:t>R$ 1.263.492,89</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.262.371,86</x:t>
   </x:si>
   <x:si>
     <x:t>20/08/2026</x:t>
@@ -163,16 +163,16 @@
     <x:t>R$ 1.500.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.501.976,87</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.501.532,07</x:t>
+    <x:t>R$ 1.503.956,33</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.503.066,15</x:t>
   </x:si>
   <x:si>
     <x:t>9,81%|Fundos de Investimento</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 467.700,02</x:t>
+    <x:t>R$ 468.429,66</x:t>
   </x:si>
   <x:si>
     <x:t>9,80%|Fundos de Renda Fixa Pós-Fixado</x:t>
@@ -193,10 +193,10 @@
     <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
   </x:si>
   <x:si>
-    <x:t>24/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 272,16</x:t>
+    <x:t>27/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 272,58</x:t>
   </x:si>
   <x:si>
     <x:t>1.718,50</x:t>
@@ -205,7 +205,7 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 467.092,23</x:t>
+    <x:t>R$ 467.299,16</x:t>
   </x:si>
   <x:si>
     <x:t>0,01%|Saldo projetado</x:t>
@@ -849,10 +849,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>4768370.49526831</x:v>
+        <x:v>4774772.00730185</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>4767853.09526831</x:v>
+        <x:v>4774254.60730185</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>517.4</x:v>

--- a/data/positions/Posição Consolidada - 11370136.xlsx
+++ b/data/positions/Posição Consolidada - 11370136.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 11370136 | 28/08/2026, 09:34</x:t>
+    <x:t>Conta: 11370136 | 31/08/2026, 17:50</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>32,2%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.538.375,72</x:t>
-  </x:si>
-  <x:si>
-    <x:t>32,20%|Pós-Fixada</x:t>
+    <x:t>50,0%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.539.052,79</x:t>
+  </x:si>
+  <x:si>
+    <x:t>50,00%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -94,10 +94,10 @@
     <x:t>R$ 1.222.011,09</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.226.335,80</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.223.481,49</x:t>
+    <x:t>R$ 1.226.877,47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.224.152,30</x:t>
   </x:si>
   <x:si>
     <x:t>LCI CEF - NOV/2026</x:t>
@@ -115,67 +115,46 @@
     <x:t>R$ 310.958,77</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 312.039,92</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 311.326,36</x:t>
-  </x:si>
-  <x:si>
-    <x:t>58,0%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.767.449,23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>57,90%|Pós-Fixada</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18/09/2026</x:t>
+    <x:t>R$ 312.175,33</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 311.494,06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>34,7%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.065.939,95</x:t>
+  </x:si>
+  <x:si>
+    <x:t>34,60%|Pós-Fixada</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29/09/2026</x:t>
   </x:si>
   <x:si>
     <x:t>85,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>871,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.258.510,52</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.263.492,89</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.262.371,86</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.063.829,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.500.000,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.503.956,33</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.503.066,15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9,81%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 468.429,66</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9,80%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>773,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.065.472,09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.065.834,68</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15,2%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 468.914,76</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15,20%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -193,10 +172,10 @@
     <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
   </x:si>
   <x:si>
-    <x:t>27/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 272,58</x:t>
+    <x:t>31/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 272,86</x:t>
   </x:si>
   <x:si>
     <x:t>1.718,50</x:t>
@@ -205,13 +184,13 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 467.299,16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,01%|Saldo projetado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 517,40</x:t>
+    <x:t>R$ 467.593,58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,06%|Saldo projetado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.743,15</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -241,7 +220,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>517,4</x:t>
+    <x:t>1743,15</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -789,10 +768,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K27"/>
+  <x:dimension ref="A1:K26"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="36.996339" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="38.282054" style="0" customWidth="1"/>
     <x:col min="2" max="11" width="24.930625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -849,13 +828,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>4774772.00730185</x:v>
+        <x:v>3075650.65118428</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>4774254.60730185</x:v>
+        <x:v>3073907.50118428</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>517.4</x:v>
+        <x:v>1743.15</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -1100,271 +1079,242 @@
       <x:c r="K15" s="3"/>
     </x:row>
     <x:row r="16" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A16" s="12"/>
-      <x:c r="B16" s="12" t="s">
+      <x:c r="A16" s="13"/>
+      <x:c r="B16" s="13" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C16" s="12"/>
-      <x:c r="D16" s="12" t="s">
+      <x:c r="C16" s="13"/>
+      <x:c r="D16" s="13" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="E16" s="12" t="s">
+      <x:c r="E16" s="13" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="F16" s="12" t="s">
+      <x:c r="F16" s="13" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="G16" s="12" t="s">
+      <x:c r="G16" s="13" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="H16" s="12" t="s">
+      <x:c r="H16" s="13" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="I16" s="12" t="s">
+      <x:c r="I16" s="13" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="J16" s="13" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="J16" s="12" t="s">
+      <x:c r="K16" s="3"/>
+    </x:row>
+    <x:row r="17" spans="1:11">
+      <x:c r="A17" s="4"/>
+      <x:c r="B17" s="4"/>
+      <x:c r="C17" s="4"/>
+      <x:c r="D17" s="4"/>
+      <x:c r="E17" s="4"/>
+      <x:c r="F17" s="4"/>
+      <x:c r="G17" s="4"/>
+      <x:c r="H17" s="4"/>
+      <x:c r="I17" s="4"/>
+      <x:c r="J17" s="4"/>
+      <x:c r="K17" s="4"/>
+    </x:row>
+    <x:row r="18" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A18" s="8" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="K16" s="3"/>
-    </x:row>
-    <x:row r="17" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A17" s="13"/>
-      <x:c r="B17" s="13" t="s">
+      <x:c r="B18" s="9"/>
+      <x:c r="C18" s="9"/>
+      <x:c r="D18" s="9"/>
+      <x:c r="E18" s="9"/>
+      <x:c r="F18" s="9"/>
+      <x:c r="G18" s="10" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="C17" s="13"/>
-      <x:c r="D17" s="13" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E17" s="13" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="F17" s="13" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="G17" s="13" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H17" s="13" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="I17" s="13" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="J17" s="13" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="K17" s="3"/>
-    </x:row>
-    <x:row r="18" spans="1:11">
-      <x:c r="A18" s="4"/>
-      <x:c r="B18" s="4"/>
-      <x:c r="C18" s="4"/>
-      <x:c r="D18" s="4"/>
-      <x:c r="E18" s="4"/>
-      <x:c r="F18" s="4"/>
-      <x:c r="G18" s="4"/>
-      <x:c r="H18" s="4"/>
-      <x:c r="I18" s="4"/>
-      <x:c r="J18" s="4"/>
-      <x:c r="K18" s="4"/>
-    </x:row>
-    <x:row r="19" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A19" s="8" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="B19" s="9"/>
-      <x:c r="C19" s="9"/>
-      <x:c r="D19" s="9"/>
-      <x:c r="E19" s="9"/>
-      <x:c r="F19" s="9"/>
-      <x:c r="G19" s="10" t="s">
-        <x:v>52</x:v>
-      </x:c>
+      <x:c r="H18" s="3"/>
+      <x:c r="I18" s="3"/>
+      <x:c r="J18" s="3"/>
+      <x:c r="K18" s="3"/>
+    </x:row>
+    <x:row r="19" spans="1:11">
+      <x:c r="A19" s="4"/>
+      <x:c r="B19" s="4"/>
+      <x:c r="C19" s="4"/>
+      <x:c r="D19" s="4"/>
+      <x:c r="E19" s="4"/>
+      <x:c r="F19" s="4"/>
+      <x:c r="G19" s="4"/>
       <x:c r="H19" s="3"/>
       <x:c r="I19" s="3"/>
       <x:c r="J19" s="3"/>
       <x:c r="K19" s="3"/>
     </x:row>
-    <x:row r="20" spans="1:11">
-      <x:c r="A20" s="4"/>
-      <x:c r="B20" s="4"/>
-      <x:c r="C20" s="4"/>
-      <x:c r="D20" s="4"/>
-      <x:c r="E20" s="4"/>
-      <x:c r="F20" s="4"/>
-      <x:c r="G20" s="4"/>
+    <x:row r="20" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A20" s="11" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B20" s="11" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C20" s="11" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D20" s="11" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E20" s="11" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F20" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G20" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
       <x:c r="H20" s="3"/>
       <x:c r="I20" s="3"/>
       <x:c r="J20" s="3"/>
       <x:c r="K20" s="3"/>
     </x:row>
-    <x:row r="21" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A21" s="11" t="s">
+    <x:row r="21" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A21" s="13" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B21" s="13" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C21" s="13" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="B21" s="11" t="s">
+      <x:c r="D21" s="13" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="C21" s="11" t="s">
+      <x:c r="E21" s="13" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="D21" s="11" t="s">
+      <x:c r="F21" s="13" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G21" s="13" t="s">
         <x:v>56</x:v>
-      </x:c>
-      <x:c r="E21" s="11" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="F21" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G21" s="11" t="s">
-        <x:v>17</x:v>
       </x:c>
       <x:c r="H21" s="3"/>
       <x:c r="I21" s="3"/>
       <x:c r="J21" s="3"/>
       <x:c r="K21" s="3"/>
     </x:row>
-    <x:row r="22" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A22" s="13" t="s">
+    <x:row r="22" spans="1:11">
+      <x:c r="A22" s="4"/>
+      <x:c r="B22" s="4"/>
+      <x:c r="C22" s="4"/>
+      <x:c r="D22" s="4"/>
+      <x:c r="E22" s="4"/>
+      <x:c r="F22" s="4"/>
+      <x:c r="G22" s="4"/>
+      <x:c r="H22" s="4"/>
+      <x:c r="I22" s="4"/>
+      <x:c r="J22" s="4"/>
+      <x:c r="K22" s="4"/>
+    </x:row>
+    <x:row r="23" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A23" s="8" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B23" s="9"/>
+      <x:c r="C23" s="9"/>
+      <x:c r="D23" s="9"/>
+      <x:c r="E23" s="9"/>
+      <x:c r="F23" s="9"/>
+      <x:c r="G23" s="9"/>
+      <x:c r="H23" s="9"/>
+      <x:c r="I23" s="9"/>
+      <x:c r="J23" s="9"/>
+      <x:c r="K23" s="10" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="B22" s="13" t="s">
+    </x:row>
+    <x:row r="24" spans="1:11">
+      <x:c r="A24" s="4"/>
+      <x:c r="B24" s="4"/>
+      <x:c r="C24" s="4"/>
+      <x:c r="D24" s="4"/>
+      <x:c r="E24" s="4"/>
+      <x:c r="F24" s="4"/>
+      <x:c r="G24" s="4"/>
+      <x:c r="H24" s="4"/>
+      <x:c r="I24" s="4"/>
+      <x:c r="J24" s="4"/>
+      <x:c r="K24" s="4"/>
+    </x:row>
+    <x:row r="25" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A25" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B25" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C25" s="11" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="C22" s="13" t="s">
+      <x:c r="D25" s="11" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="D22" s="13" t="s">
+      <x:c r="E25" s="11" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="E22" s="13" t="s">
+      <x:c r="F25" s="11" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="F22" s="13" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="G22" s="13" t="s">
+      <x:c r="G25" s="11" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="H22" s="3"/>
-      <x:c r="I22" s="3"/>
-      <x:c r="J22" s="3"/>
-      <x:c r="K22" s="3"/>
-    </x:row>
-    <x:row r="23" spans="1:11">
-      <x:c r="A23" s="4"/>
-      <x:c r="B23" s="4"/>
-      <x:c r="C23" s="4"/>
-      <x:c r="D23" s="4"/>
-      <x:c r="E23" s="4"/>
-      <x:c r="F23" s="4"/>
-      <x:c r="G23" s="4"/>
-      <x:c r="H23" s="4"/>
-      <x:c r="I23" s="4"/>
-      <x:c r="J23" s="4"/>
-      <x:c r="K23" s="4"/>
-    </x:row>
-    <x:row r="24" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A24" s="8" t="s">
+      <x:c r="H25" s="11" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="B24" s="9"/>
-      <x:c r="C24" s="9"/>
-      <x:c r="D24" s="9"/>
-      <x:c r="E24" s="9"/>
-      <x:c r="F24" s="9"/>
-      <x:c r="G24" s="9"/>
-      <x:c r="H24" s="9"/>
-      <x:c r="I24" s="9"/>
-      <x:c r="J24" s="9"/>
-      <x:c r="K24" s="10" t="s">
+      <x:c r="I25" s="11" t="s">
         <x:v>65</x:v>
       </x:c>
-    </x:row>
-    <x:row r="25" spans="1:11">
-      <x:c r="A25" s="4"/>
-      <x:c r="B25" s="4"/>
-      <x:c r="C25" s="4"/>
-      <x:c r="D25" s="4"/>
-      <x:c r="E25" s="4"/>
-      <x:c r="F25" s="4"/>
-      <x:c r="G25" s="4"/>
-      <x:c r="H25" s="4"/>
-      <x:c r="I25" s="4"/>
-      <x:c r="J25" s="4"/>
-      <x:c r="K25" s="4"/>
-    </x:row>
-    <x:row r="26" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A26" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B26" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C26" s="11" t="s">
+      <x:c r="J25" s="11" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="D26" s="11" t="s">
+      <x:c r="K25" s="11" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="E26" s="11" t="s">
+    </x:row>
+    <x:row r="26" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A26" s="13" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="F26" s="11" t="s">
+      <x:c r="B26" s="13" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="G26" s="11" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="H26" s="11" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="I26" s="11" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="J26" s="11" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="K26" s="11" t="s">
-        <x:v>74</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A27" s="13" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="B27" s="13" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="C27" s="13" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="D27" s="13" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="E27" s="13" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="F27" s="13" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="G27" s="13" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="H27" s="13" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="I27" s="13" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="J27" s="13" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="K27" s="13" t="s">
-        <x:v>76</x:v>
+      <x:c r="C26" s="13" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D26" s="13" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="E26" s="13" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="F26" s="13" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="G26" s="13" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="H26" s="13" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="I26" s="13" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="J26" s="13" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="K26" s="13" t="s">
+        <x:v>69</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1373,8 +1323,8 @@
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="A7:F7"/>
     <x:mergeCell ref="A13:F13"/>
-    <x:mergeCell ref="A19:F19"/>
-    <x:mergeCell ref="A24:J24"/>
+    <x:mergeCell ref="A18:F18"/>
+    <x:mergeCell ref="A23:J23"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 11370136.xlsx
+++ b/data/positions/Posição Consolidada - 11370136.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 11370136 | 31/08/2026, 17:50</x:t>
+    <x:t>Conta: 11370136 | 01/09/2026, 15:59</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>50,0%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.539.052,79</x:t>
-  </x:si>
-  <x:si>
-    <x:t>50,00%|Pós-Fixada</x:t>
+    <x:t>55,4%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.539.730,16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>55,40%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -94,10 +94,10 @@
     <x:t>R$ 1.222.011,09</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.226.877,47</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.224.152,30</x:t>
+    <x:t>R$ 1.227.419,37</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.224.552,98</x:t>
   </x:si>
   <x:si>
     <x:t>LCI CEF - NOV/2026</x:t>
@@ -115,19 +115,19 @@
     <x:t>R$ 310.958,77</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 312.175,33</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 311.494,06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>34,7%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.065.939,95</x:t>
-  </x:si>
-  <x:si>
-    <x:t>34,60%|Pós-Fixada</x:t>
+    <x:t>R$ 312.310,79</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 311.594,22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27,6%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 765.661,64</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27,50%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>28/08/2026</x:t>
@@ -139,22 +139,22 @@
     <x:t>85,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>773,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.065.472,09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.065.834,68</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15,2%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 468.914,76</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15,20%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>555,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 764.989,66</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 765.510,45</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16,9%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 469.154,18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16,80%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -172,10 +172,10 @@
     <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
   </x:si>
   <x:si>
-    <x:t>31/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 272,86</x:t>
+    <x:t>01/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 273,00</x:t>
   </x:si>
   <x:si>
     <x:t>1.718,50</x:t>
@@ -184,13 +184,13 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 467.593,58</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,06%|Saldo projetado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.743,15</x:t>
+    <x:t>R$ 467.734,58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,09%|Saldo projetado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.430,14</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -220,7 +220,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>1743,15</x:t>
+    <x:t>2430,14</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -828,13 +828,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>3075650.65118428</x:v>
+        <x:v>2776976.12234587</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>3073907.50118428</x:v>
+        <x:v>2774545.98234587</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>1743.15</x:v>
+        <x:v>2430.14</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>

--- a/data/positions/Posição Consolidada - 11370136.xlsx
+++ b/data/positions/Posição Consolidada - 11370136.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 11370136 | 01/09/2026, 15:59</x:t>
+    <x:t>Conta: 11370136 | 04/09/2026, 14:15</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>55,4%|Renda Fixa</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.539.730,16</x:t>
+    <x:t>R$ 1.541.764,06</x:t>
   </x:si>
   <x:si>
     <x:t>55,40%|Pós-Fixada</x:t>
@@ -94,10 +94,10 @@
     <x:t>R$ 1.222.011,09</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.227.419,37</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.224.552,98</x:t>
+    <x:t>R$ 1.229.046,51</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.226.021,28</x:t>
   </x:si>
   <x:si>
     <x:t>LCI CEF - NOV/2026</x:t>
@@ -115,16 +115,16 @@
     <x:t>R$ 310.958,77</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 312.310,79</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 311.594,22</x:t>
+    <x:t>R$ 312.717,55</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 311.961,28</x:t>
   </x:si>
   <x:si>
     <x:t>27,6%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 765.661,64</x:t>
+    <x:t>R$ 766.670,71</x:t>
   </x:si>
   <x:si>
     <x:t>27,50%|Pós-Fixada</x:t>
@@ -145,13 +145,13 @@
     <x:t>R$ 764.989,66</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 765.510,45</x:t>
+    <x:t>R$ 766.292,47</x:t>
   </x:si>
   <x:si>
     <x:t>16,9%|Fundos de Investimento</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 469.154,18</x:t>
+    <x:t>R$ 469.869,10</x:t>
   </x:si>
   <x:si>
     <x:t>16,80%|Fundos de Renda Fixa Pós-Fixado</x:t>
@@ -172,10 +172,10 @@
     <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
   </x:si>
   <x:si>
-    <x:t>01/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 273,00</x:t>
+    <x:t>04/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 273,42</x:t>
   </x:si>
   <x:si>
     <x:t>1.718,50</x:t>
@@ -184,7 +184,7 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 467.734,58</x:t>
+    <x:t>R$ 468.200,72</x:t>
   </x:si>
   <x:si>
     <x:t>0,09%|Saldo projetado</x:t>
@@ -828,10 +828,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>2776976.12234587</x:v>
+        <x:v>2780734.01311854</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>2774545.98234587</x:v>
+        <x:v>2778303.87311854</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>2430.14</x:v>

--- a/data/positions/Posição Consolidada - 11370136.xlsx
+++ b/data/positions/Posição Consolidada - 11370136.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 11370136 | 04/09/2026, 14:15</x:t>
+    <x:t>Conta: 11370136 | 10/09/2026, 14:05</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>55,4%|Renda Fixa</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.541.764,06</x:t>
+    <x:t>R$ 1.543.800,65</x:t>
   </x:si>
   <x:si>
     <x:t>55,40%|Pós-Fixada</x:t>
@@ -94,10 +94,10 @@
     <x:t>R$ 1.222.011,09</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.229.046,51</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.226.021,28</x:t>
+    <x:t>R$ 1.230.675,82</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.228.682,93</x:t>
   </x:si>
   <x:si>
     <x:t>LCI CEF - NOV/2026</x:t>
@@ -115,16 +115,16 @@
     <x:t>R$ 310.958,77</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 312.717,55</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 311.961,28</x:t>
+    <x:t>R$ 313.124,83</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 312.626,64</x:t>
   </x:si>
   <x:si>
     <x:t>27,6%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 766.670,71</x:t>
+    <x:t>R$ 767.681,11</x:t>
   </x:si>
   <x:si>
     <x:t>27,50%|Pós-Fixada</x:t>
@@ -145,16 +145,16 @@
     <x:t>R$ 764.989,66</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 766.292,47</x:t>
+    <x:t>R$ 767.075,53</x:t>
   </x:si>
   <x:si>
     <x:t>16,9%|Fundos de Investimento</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 469.869,10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16,80%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>R$ 470.579,70</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16,90%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -172,10 +172,10 @@
     <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
   </x:si>
   <x:si>
-    <x:t>04/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 273,42</x:t>
+    <x:t>10/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 273,83</x:t>
   </x:si>
   <x:si>
     <x:t>1.718,50</x:t>
@@ -184,7 +184,7 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 468.200,72</x:t>
+    <x:t>R$ 469.052,96</x:t>
   </x:si>
   <x:si>
     <x:t>0,09%|Saldo projetado</x:t>
@@ -828,10 +828,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>2780734.01311854</x:v>
+        <x:v>2784491.60055752</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>2778303.87311854</x:v>
+        <x:v>2782061.46055752</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>2430.14</x:v>

--- a/data/positions/Posição Consolidada - 11370136.xlsx
+++ b/data/positions/Posição Consolidada - 11370136.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 11370136 | 10/09/2026, 14:05</x:t>
+    <x:t>Conta: 11370136 | 16/09/2026, 08:43</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>55,4%|Renda Fixa</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.543.800,65</x:t>
+    <x:t>R$ 1.546.520,28</x:t>
   </x:si>
   <x:si>
     <x:t>55,40%|Pós-Fixada</x:t>
@@ -94,10 +94,10 @@
     <x:t>R$ 1.222.011,09</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.230.675,82</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.228.682,93</x:t>
+    <x:t>R$ 1.232.851,58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.232.526,37</x:t>
   </x:si>
   <x:si>
     <x:t>LCI CEF - NOV/2026</x:t>
@@ -115,16 +115,16 @@
     <x:t>R$ 310.958,77</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 313.124,83</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 312.626,64</x:t>
+    <x:t>R$ 313.668,70</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 313.587,40</x:t>
   </x:si>
   <x:si>
     <x:t>27,6%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 767.681,11</x:t>
+    <x:t>R$ 769.030,39</x:t>
   </x:si>
   <x:si>
     <x:t>27,50%|Pós-Fixada</x:t>
@@ -145,16 +145,16 @@
     <x:t>R$ 764.989,66</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 767.075,53</x:t>
+    <x:t>R$ 768.121,23</x:t>
   </x:si>
   <x:si>
     <x:t>16,9%|Fundos de Investimento</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 470.579,70</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16,90%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>R$ 471.316,12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16,80%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -172,10 +172,10 @@
     <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
   </x:si>
   <x:si>
-    <x:t>10/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 273,83</x:t>
+    <x:t>15/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 274,26</x:t>
   </x:si>
   <x:si>
     <x:t>1.718,50</x:t>
@@ -184,13 +184,13 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 469.052,96</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,09%|Saldo projetado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.430,14</x:t>
+    <x:t>R$ 470.010,50</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,08%|Saldo projetado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.249,04</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -220,7 +220,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>2430,14</x:t>
+    <x:t>2249,04</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -828,13 +828,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>2784491.60055752</x:v>
+        <x:v>2789115.82779081</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>2782061.46055752</x:v>
+        <x:v>2786866.78779081</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>2430.14</x:v>
+        <x:v>2249.04</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>

--- a/data/positions/Posição Consolidada - 11370136.xlsx
+++ b/data/positions/Posição Consolidada - 11370136.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 11370136 | 16/09/2026, 08:43</x:t>
+    <x:t>Conta: 11370136 | 21/09/2026, 16:40</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>55,4%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.546.520,28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>55,40%|Pós-Fixada</x:t>
+    <x:t>34,5%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.548.540,15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>34,40%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -94,10 +94,7 @@
     <x:t>R$ 1.222.011,09</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.232.851,58</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.232.526,37</x:t>
+    <x:t>R$ 1.234.467,53</x:t>
   </x:si>
   <x:si>
     <x:t>LCI CEF - NOV/2026</x:t>
@@ -115,46 +112,43 @@
     <x:t>R$ 310.958,77</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 313.668,70</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 313.587,40</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27,6%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 769.030,39</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27,50%|Pós-Fixada</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29/09/2026</x:t>
+    <x:t>R$ 314.072,62</x:t>
+  </x:si>
+  <x:si>
+    <x:t>55,0%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.473.051,34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>55,00%|Pós-Fixada</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16/10/2026</x:t>
   </x:si>
   <x:si>
     <x:t>85,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>555,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 764.989,66</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 768.121,23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16,9%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 471.316,12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16,80%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>1.727.914,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.470.917,50</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.472.571,23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10,5%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 472.276,87</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10,50%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -172,10 +166,10 @@
     <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
   </x:si>
   <x:si>
-    <x:t>15/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 274,26</x:t>
+    <x:t>21/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 274,82</x:t>
   </x:si>
   <x:si>
     <x:t>1.718,50</x:t>
@@ -184,13 +178,13 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 470.010,50</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,08%|Saldo projetado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.249,04</x:t>
+    <x:t>R$ 471.089,58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,01%|Saldo projetado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 250,21</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -220,7 +214,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>2249,04</x:t>
+    <x:t>250,21</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -828,13 +822,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>2789115.82779081</x:v>
+        <x:v>4494118.57006331</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>2786866.78779081</x:v>
+        <x:v>4493868.36006331</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>2249.04</x:v>
+        <x:v>250.21</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -965,25 +959,25 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="J10" s="12" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K10" s="3"/>
     </x:row>
     <x:row r="11" spans="1:11" ht="30" customHeight="1">
       <x:c r="A11" s="13" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B11" s="13" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C11" s="13" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D11" s="13" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="D11" s="13" t="s">
+      <x:c r="E11" s="13" t="s">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="E11" s="13" t="s">
-        <x:v>31</x:v>
       </x:c>
       <x:c r="F11" s="13" t="s">
         <x:v>23</x:v>
@@ -992,13 +986,13 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="H11" s="13" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I11" s="13" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="I11" s="13" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="J11" s="13" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="K11" s="3"/>
     </x:row>
@@ -1017,7 +1011,7 @@
     </x:row>
     <x:row r="13" spans="1:11" ht="45" customHeight="1">
       <x:c r="A13" s="8" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B13" s="9"/>
       <x:c r="C13" s="9"/>
@@ -1025,7 +1019,7 @@
       <x:c r="E13" s="9"/>
       <x:c r="F13" s="9"/>
       <x:c r="G13" s="10" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H13" s="3"/>
       <x:c r="I13" s="3"/>
@@ -1047,7 +1041,7 @@
     </x:row>
     <x:row r="15" spans="1:11" ht="35.1" customHeight="1">
       <x:c r="A15" s="11" t="s">
-        <x:v>37</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B15" s="11" t="s">
         <x:v>9</x:v>
@@ -1081,29 +1075,29 @@
     <x:row r="16" spans="1:11" ht="30" customHeight="1">
       <x:c r="A16" s="13"/>
       <x:c r="B16" s="13" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C16" s="13"/>
       <x:c r="D16" s="13" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E16" s="13" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F16" s="13" t="s">
         <x:v>39</x:v>
-      </x:c>
-      <x:c r="E16" s="13" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="F16" s="13" t="s">
-        <x:v>41</x:v>
       </x:c>
       <x:c r="G16" s="13" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="H16" s="13" t="s">
-        <x:v>42</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="I16" s="13" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="J16" s="13" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K16" s="3"/>
     </x:row>
@@ -1122,7 +1116,7 @@
     </x:row>
     <x:row r="18" spans="1:11" ht="45" customHeight="1">
       <x:c r="A18" s="8" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B18" s="9"/>
       <x:c r="C18" s="9"/>
@@ -1130,7 +1124,7 @@
       <x:c r="E18" s="9"/>
       <x:c r="F18" s="9"/>
       <x:c r="G18" s="10" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H18" s="3"/>
       <x:c r="I18" s="3"/>
@@ -1152,19 +1146,19 @@
     </x:row>
     <x:row r="20" spans="1:11" ht="35.1" customHeight="1">
       <x:c r="A20" s="11" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B20" s="11" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C20" s="11" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="B20" s="11" t="s">
+      <x:c r="D20" s="11" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="C20" s="11" t="s">
+      <x:c r="E20" s="11" t="s">
         <x:v>48</x:v>
-      </x:c>
-      <x:c r="D20" s="11" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E20" s="11" t="s">
-        <x:v>50</x:v>
       </x:c>
       <x:c r="F20" s="11" t="s">
         <x:v>16</x:v>
@@ -1179,25 +1173,25 @@
     </x:row>
     <x:row r="21" spans="1:11" ht="30" customHeight="1">
       <x:c r="A21" s="13" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B21" s="13" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C21" s="13" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="B21" s="13" t="s">
+      <x:c r="D21" s="13" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C21" s="13" t="s">
+      <x:c r="E21" s="13" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="D21" s="13" t="s">
+      <x:c r="F21" s="13" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G21" s="13" t="s">
         <x:v>54</x:v>
-      </x:c>
-      <x:c r="E21" s="13" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="F21" s="13" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="G21" s="13" t="s">
-        <x:v>56</x:v>
       </x:c>
       <x:c r="H21" s="3"/>
       <x:c r="I21" s="3"/>
@@ -1219,7 +1213,7 @@
     </x:row>
     <x:row r="23" spans="1:11" ht="45" customHeight="1">
       <x:c r="A23" s="8" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B23" s="9"/>
       <x:c r="C23" s="9"/>
@@ -1231,7 +1225,7 @@
       <x:c r="I23" s="9"/>
       <x:c r="J23" s="9"/>
       <x:c r="K23" s="10" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
@@ -1255,66 +1249,66 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C25" s="11" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D25" s="11" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E25" s="11" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="D25" s="11" t="s">
+      <x:c r="F25" s="11" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="E25" s="11" t="s">
+      <x:c r="G25" s="11" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="F25" s="11" t="s">
+      <x:c r="H25" s="11" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="G25" s="11" t="s">
+      <x:c r="I25" s="11" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="H25" s="11" t="s">
+      <x:c r="J25" s="11" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="I25" s="11" t="s">
+      <x:c r="K25" s="11" t="s">
         <x:v>65</x:v>
-      </x:c>
-      <x:c r="J25" s="11" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="K25" s="11" t="s">
-        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11" ht="30" customHeight="1">
       <x:c r="A26" s="13" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B26" s="13" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C26" s="13" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D26" s="13" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E26" s="13" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F26" s="13" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="G26" s="13" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H26" s="13" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="I26" s="13" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="J26" s="13" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="K26" s="13" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/positions/Posição Consolidada - 11370136.xlsx
+++ b/data/positions/Posição Consolidada - 11370136.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 11370136 | 21/09/2026, 16:40</x:t>
+    <x:t>Conta: 11370136 | 23/09/2026, 09:36</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>34,5%|Renda Fixa</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.548.540,15</x:t>
+    <x:t>R$ 1.549.880,52</x:t>
   </x:si>
   <x:si>
     <x:t>34,40%|Pós-Fixada</x:t>
@@ -94,7 +94,7 @@
     <x:t>R$ 1.222.011,09</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.234.467,53</x:t>
+    <x:t>R$ 1.235.539,87</x:t>
   </x:si>
   <x:si>
     <x:t>LCI CEF - NOV/2026</x:t>
@@ -112,13 +112,13 @@
     <x:t>R$ 310.958,77</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 314.072,62</x:t>
+    <x:t>R$ 314.340,66</x:t>
   </x:si>
   <x:si>
     <x:t>55,0%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.473.051,34</x:t>
+    <x:t>R$ 2.475.187,02</x:t>
   </x:si>
   <x:si>
     <x:t>55,00%|Pós-Fixada</x:t>
@@ -139,13 +139,13 @@
     <x:t>R$ 2.470.917,50</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.472.571,23</x:t>
+    <x:t>R$ 2.474.226,38</x:t>
   </x:si>
   <x:si>
     <x:t>10,5%|Fundos de Investimento</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 472.276,87</x:t>
+    <x:t>R$ 472.513,12</x:t>
   </x:si>
   <x:si>
     <x:t>10,50%|Fundos de Renda Fixa Pós-Fixado</x:t>
@@ -166,10 +166,10 @@
     <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
   </x:si>
   <x:si>
-    <x:t>21/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 274,82</x:t>
+    <x:t>22/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 274,96</x:t>
   </x:si>
   <x:si>
     <x:t>1.718,50</x:t>
@@ -178,7 +178,7 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 471.089,58</x:t>
+    <x:t>R$ 471.272,67</x:t>
   </x:si>
   <x:si>
     <x:t>0,01%|Saldo projetado</x:t>
@@ -822,10 +822,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>4494118.57006331</x:v>
+        <x:v>4497830.87718603</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>4493868.36006331</x:v>
+        <x:v>4497580.66718603</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>250.21</x:v>

--- a/data/positions/Posição Consolidada - 11370136.xlsx
+++ b/data/positions/Posição Consolidada - 11370136.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 11370136 | 23/09/2026, 09:36</x:t>
+    <x:t>Conta: 11370136 | 30/09/2026, 08:52</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>34,5%|Renda Fixa</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.549.880,52</x:t>
+    <x:t>R$ 1.553.236,53</x:t>
   </x:si>
   <x:si>
     <x:t>34,40%|Pós-Fixada</x:t>
@@ -94,7 +94,7 @@
     <x:t>R$ 1.222.011,09</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.235.539,87</x:t>
+    <x:t>R$ 1.238.224,79</x:t>
   </x:si>
   <x:si>
     <x:t>LCI CEF - NOV/2026</x:t>
@@ -112,13 +112,13 @@
     <x:t>R$ 310.958,77</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 314.340,66</x:t>
+    <x:t>R$ 315.011,75</x:t>
   </x:si>
   <x:si>
     <x:t>55,0%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.475.187,02</x:t>
+    <x:t>R$ 2.480.534,30</x:t>
   </x:si>
   <x:si>
     <x:t>55,00%|Pós-Fixada</x:t>
@@ -139,13 +139,13 @@
     <x:t>R$ 2.470.917,50</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.474.226,38</x:t>
+    <x:t>R$ 2.478.370,52</x:t>
   </x:si>
   <x:si>
     <x:t>10,5%|Fundos de Investimento</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 472.513,12</x:t>
+    <x:t>R$ 473.642,63</x:t>
   </x:si>
   <x:si>
     <x:t>10,50%|Fundos de Renda Fixa Pós-Fixado</x:t>
@@ -166,10 +166,10 @@
     <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
   </x:si>
   <x:si>
-    <x:t>22/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 274,96</x:t>
+    <x:t>29/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 275,61</x:t>
   </x:si>
   <x:si>
     <x:t>1.718,50</x:t>
@@ -178,7 +178,7 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 471.272,67</x:t>
+    <x:t>R$ 472.148,04</x:t>
   </x:si>
   <x:si>
     <x:t>0,01%|Saldo projetado</x:t>
@@ -822,10 +822,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>4497830.87718603</x:v>
+        <x:v>4507663.66898954</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>4497580.66718603</x:v>
+        <x:v>4507413.45898954</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>250.21</x:v>

--- a/data/positions/Posição Consolidada - 11370136.xlsx
+++ b/data/positions/Posição Consolidada - 11370136.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 11370136 | 30/09/2026, 08:52</x:t>
+    <x:t>Conta: 11370136 | 13/10/2026, 11:09</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>34,5%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.553.236,53</x:t>
-  </x:si>
-  <x:si>
-    <x:t>34,40%|Pós-Fixada</x:t>
+    <x:t>43,1%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.558.621,27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43,00%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -94,7 +94,7 @@
     <x:t>R$ 1.222.011,09</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.238.224,79</x:t>
+    <x:t>R$ 1.242.532,80</x:t>
   </x:si>
   <x:si>
     <x:t>LCI CEF - NOV/2026</x:t>
@@ -112,16 +112,16 @@
     <x:t>R$ 310.958,77</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 315.011,75</x:t>
-  </x:si>
-  <x:si>
-    <x:t>55,0%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.480.534,30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>55,00%|Pós-Fixada</x:t>
+    <x:t>R$ 316.088,47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13,3%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 479.440,47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13,20%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>17/09/2026</x:t>
@@ -133,22 +133,22 @@
     <x:t>85,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>1.727.914,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.470.917,50</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.478.370,52</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10,5%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 473.642,63</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10,50%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>332.822,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 475.935,55</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 478.651,86</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43,7%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.579.193,99</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43,60%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -166,25 +166,25 @@
     <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
   </x:si>
   <x:si>
-    <x:t>29/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 275,61</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.718,50</x:t>
+    <x:t>13/10/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 276,87</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5.703,73</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 472.148,04</x:t>
+    <x:t>R$ 1.574.794,73</x:t>
   </x:si>
   <x:si>
     <x:t>0,01%|Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 250,21</x:t>
+    <x:t>R$ 183,71</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -214,7 +214,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>250,21</x:t>
+    <x:t>183,71</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -822,13 +822,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>4507663.66898954</x:v>
+        <x:v>3617439.44026168</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>4507413.45898954</x:v>
+        <x:v>3617255.73026168</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>250.21</x:v>
+        <x:v>183.71</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>

--- a/data/positions/Posição Consolidada - 11370136.xlsx
+++ b/data/positions/Posição Consolidada - 11370136.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 11370136 | 13/10/2026, 11:09</x:t>
+    <x:t>Conta: 11370136 | 14/10/2026, 08:49</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>43,1%|Renda Fixa</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.558.621,27</x:t>
+    <x:t>R$ 1.559.295,68</x:t>
   </x:si>
   <x:si>
     <x:t>43,00%|Pós-Fixada</x:t>
@@ -94,7 +94,7 @@
     <x:t>R$ 1.222.011,09</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.242.532,80</x:t>
+    <x:t>R$ 1.243.072,35</x:t>
   </x:si>
   <x:si>
     <x:t>LCI CEF - NOV/2026</x:t>
@@ -112,13 +112,13 @@
     <x:t>R$ 310.958,77</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 316.088,47</x:t>
+    <x:t>R$ 316.223,32</x:t>
   </x:si>
   <x:si>
     <x:t>13,3%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 479.440,47</x:t>
+    <x:t>R$ 479.647,44</x:t>
   </x:si>
   <x:si>
     <x:t>13,20%|Pós-Fixada</x:t>
@@ -139,10 +139,10 @@
     <x:t>R$ 475.935,55</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 478.651,86</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43,7%|Fundos de Investimento</x:t>
+    <x:t>R$ 478.812,27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43,6%|Fundos de Investimento</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 1.579.193,99</x:t>
@@ -181,10 +181,10 @@
     <x:t>R$ 1.574.794,73</x:t>
   </x:si>
   <x:si>
-    <x:t>0,01%|Saldo projetado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 183,71</x:t>
+    <x:t>0,02%|Saldo projetado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 710,42</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -218,6 +218,9 @@
   </x:si>
   <x:si>
     <x:t>0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>526,71</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -822,16 +825,16 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>3617439.44026168</x:v>
+        <x:v>3618847.52590228</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>3617255.73026168</x:v>
+        <x:v>3618137.10590228</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>183.71</x:v>
       </x:c>
       <x:c r="D4" s="7">
-        <x:v>0</x:v>
+        <x:v>526.71</x:v>
       </x:c>
       <x:c r="E4" s="4"/>
       <x:c r="F4" s="4"/>
@@ -1296,10 +1299,10 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="G26" s="13" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H26" s="13" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="I26" s="13" t="s">
         <x:v>67</x:v>

--- a/data/positions/Posição Consolidada - 11370136.xlsx
+++ b/data/positions/Posição Consolidada - 11370136.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 11370136 | 14/10/2026, 08:49</x:t>
+    <x:t>Conta: 11370136 | 27/10/2026, 19:00</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>43,1%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.559.295,68</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43,00%|Pós-Fixada</x:t>
+    <x:t>50,0%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.565.378,46</x:t>
+  </x:si>
+  <x:si>
+    <x:t>49,90%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -94,7 +94,7 @@
     <x:t>R$ 1.222.011,09</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.243.072,35</x:t>
+    <x:t>R$ 1.247.938,89</x:t>
   </x:si>
   <x:si>
     <x:t>LCI CEF - NOV/2026</x:t>
@@ -112,43 +112,43 @@
     <x:t>R$ 310.958,77</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 316.223,32</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13,3%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 479.647,44</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13,20%|Pós-Fixada</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16/10/2026</x:t>
+    <x:t>R$ 317.439,56</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,35%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 11.019,01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,35%|Pós-Fixada</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21/10/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25/11/2026</x:t>
   </x:si>
   <x:si>
     <x:t>85,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>332.822,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 475.935,55</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 478.812,27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43,6%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.579.193,99</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43,60%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>6.748,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 11.000,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 11.014,73</x:t>
+  </x:si>
+  <x:si>
+    <x:t>49,7%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.555.288,62</x:t>
+  </x:si>
+  <x:si>
+    <x:t>49,60%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -166,25 +166,25 @@
     <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
   </x:si>
   <x:si>
-    <x:t>13/10/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 276,87</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.703,73</x:t>
+    <x:t>27/10/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 278,22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5.590,23</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.574.794,73</x:t>
+    <x:t>R$ 1.549.898,57</x:t>
   </x:si>
   <x:si>
     <x:t>0,02%|Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 710,42</x:t>
+    <x:t>R$ 516,67</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -214,13 +214,10 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>183,71</x:t>
+    <x:t>516,67</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>526,71</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -825,16 +822,16 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>3618847.52590228</x:v>
+        <x:v>3132202.75233411</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>3618137.10590228</x:v>
+        <x:v>3131686.08233411</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>183.71</x:v>
+        <x:v>516.67</x:v>
       </x:c>
       <x:c r="D4" s="7">
-        <x:v>526.71</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E4" s="4"/>
       <x:c r="F4" s="4"/>
@@ -1299,10 +1296,10 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="G26" s="13" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H26" s="13" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="I26" s="13" t="s">
         <x:v>67</x:v>

--- a/data/positions/Posição Consolidada - 11370136.xlsx
+++ b/data/positions/Posição Consolidada - 11370136.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 11370136 | 27/10/2026, 19:00</x:t>
+    <x:t>Conta: 11370136 | 29/10/2026, 16:10</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>50,0%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.565.378,46</x:t>
-  </x:si>
-  <x:si>
-    <x:t>49,90%|Pós-Fixada</x:t>
+    <x:t>41,2%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.249.022,93</x:t>
+  </x:si>
+  <x:si>
+    <x:t>41,10%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -94,61 +94,40 @@
     <x:t>R$ 1.222.011,09</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.247.938,89</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LCI CEF - NOV/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18/11/2024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18/11/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>84,00% CDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 310.958,77</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 317.439,56</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,35%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 11.019,01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,35%|Pós-Fixada</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21/10/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25/11/2026</x:t>
+    <x:t>7,55%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 229.114,26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7,50%|Pós-Fixada</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28/10/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30/11/2026</x:t>
   </x:si>
   <x:si>
     <x:t>85,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>6.748,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 11.000,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 11.014,73</x:t>
-  </x:si>
-  <x:si>
-    <x:t>49,7%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.555.288,62</x:t>
-  </x:si>
-  <x:si>
-    <x:t>49,60%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>157.941,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 229.015,39</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 229.092,02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>51,3%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.556.769,76</x:t>
+  </x:si>
+  <x:si>
+    <x:t>51,20%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -166,10 +145,10 @@
     <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
   </x:si>
   <x:si>
-    <x:t>27/10/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 278,22</x:t>
+    <x:t>29/10/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 278,48</x:t>
   </x:si>
   <x:si>
     <x:t>5.590,23</x:t>
@@ -178,13 +157,10 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.549.898,57</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,02%|Saldo projetado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 516,67</x:t>
+    <x:t>R$ 1.551.371,59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 111,40</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -214,7 +190,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>516,67</x:t>
+    <x:t>111,4</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -410,7 +386,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="14">
+  <x:cellXfs count="13">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -456,10 +432,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -762,7 +734,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K26"/>
+  <x:dimension ref="A1:K25"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="38.282054" style="0" customWidth="1"/>
@@ -822,13 +794,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>3132202.75233411</x:v>
+        <x:v>3035018.35103208</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>3131686.08233411</x:v>
+        <x:v>3034906.95103208</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>516.67</x:v>
+        <x:v>111.4</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -956,359 +928,326 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="I10" s="12" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J10" s="12" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K10" s="3"/>
+    </x:row>
+    <x:row r="11" spans="1:11">
+      <x:c r="A11" s="4"/>
+      <x:c r="B11" s="4"/>
+      <x:c r="C11" s="4"/>
+      <x:c r="D11" s="4"/>
+      <x:c r="E11" s="4"/>
+      <x:c r="F11" s="4"/>
+      <x:c r="G11" s="4"/>
+      <x:c r="H11" s="4"/>
+      <x:c r="I11" s="4"/>
+      <x:c r="J11" s="4"/>
+      <x:c r="K11" s="4"/>
+    </x:row>
+    <x:row r="12" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A12" s="8" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="J10" s="12" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="K10" s="3"/>
-    </x:row>
-    <x:row r="11" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A11" s="13" t="s">
+      <x:c r="B12" s="9"/>
+      <x:c r="C12" s="9"/>
+      <x:c r="D12" s="9"/>
+      <x:c r="E12" s="9"/>
+      <x:c r="F12" s="9"/>
+      <x:c r="G12" s="10" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="B11" s="13" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C11" s="13" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D11" s="13" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E11" s="13" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F11" s="13" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="G11" s="13" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H11" s="13" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="I11" s="13" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="J11" s="13" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="K11" s="3"/>
-    </x:row>
-    <x:row r="12" spans="1:11">
-      <x:c r="A12" s="4"/>
-      <x:c r="B12" s="4"/>
-      <x:c r="C12" s="4"/>
-      <x:c r="D12" s="4"/>
-      <x:c r="E12" s="4"/>
-      <x:c r="F12" s="4"/>
-      <x:c r="G12" s="4"/>
-      <x:c r="H12" s="4"/>
-      <x:c r="I12" s="4"/>
-      <x:c r="J12" s="4"/>
-      <x:c r="K12" s="4"/>
-    </x:row>
-    <x:row r="13" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A13" s="8" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="B13" s="9"/>
-      <x:c r="C13" s="9"/>
-      <x:c r="D13" s="9"/>
-      <x:c r="E13" s="9"/>
-      <x:c r="F13" s="9"/>
-      <x:c r="G13" s="10" t="s">
-        <x:v>34</x:v>
-      </x:c>
+      <x:c r="H12" s="3"/>
+      <x:c r="I12" s="3"/>
+      <x:c r="J12" s="3"/>
+      <x:c r="K12" s="3"/>
+    </x:row>
+    <x:row r="13" spans="1:11">
+      <x:c r="A13" s="4"/>
+      <x:c r="B13" s="4"/>
+      <x:c r="C13" s="4"/>
+      <x:c r="D13" s="4"/>
+      <x:c r="E13" s="4"/>
+      <x:c r="F13" s="4"/>
+      <x:c r="G13" s="4"/>
       <x:c r="H13" s="3"/>
       <x:c r="I13" s="3"/>
       <x:c r="J13" s="3"/>
       <x:c r="K13" s="3"/>
     </x:row>
-    <x:row r="14" spans="1:11">
-      <x:c r="A14" s="4"/>
-      <x:c r="B14" s="4"/>
-      <x:c r="C14" s="4"/>
-      <x:c r="D14" s="4"/>
-      <x:c r="E14" s="4"/>
-      <x:c r="F14" s="4"/>
-      <x:c r="G14" s="4"/>
-      <x:c r="H14" s="3"/>
-      <x:c r="I14" s="3"/>
-      <x:c r="J14" s="3"/>
+    <x:row r="14" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A14" s="11" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B14" s="11" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D14" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F14" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G14" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H14" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I14" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J14" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
       <x:c r="K14" s="3"/>
     </x:row>
-    <x:row r="15" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A15" s="11" t="s">
+    <x:row r="15" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A15" s="12"/>
+      <x:c r="B15" s="12" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C15" s="12"/>
+      <x:c r="D15" s="12" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E15" s="12" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F15" s="12" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G15" s="12" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H15" s="12" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="I15" s="12" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="J15" s="12" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K15" s="3"/>
+    </x:row>
+    <x:row r="16" spans="1:11">
+      <x:c r="A16" s="4"/>
+      <x:c r="B16" s="4"/>
+      <x:c r="C16" s="4"/>
+      <x:c r="D16" s="4"/>
+      <x:c r="E16" s="4"/>
+      <x:c r="F16" s="4"/>
+      <x:c r="G16" s="4"/>
+      <x:c r="H16" s="4"/>
+      <x:c r="I16" s="4"/>
+      <x:c r="J16" s="4"/>
+      <x:c r="K16" s="4"/>
+    </x:row>
+    <x:row r="17" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A17" s="8" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="B15" s="11" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C15" s="11" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D15" s="11" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="E15" s="11" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="F15" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G15" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H15" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I15" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="J15" s="11" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K15" s="3"/>
-    </x:row>
-    <x:row r="16" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A16" s="13"/>
-      <x:c r="B16" s="13" t="s">
+      <x:c r="B17" s="9"/>
+      <x:c r="C17" s="9"/>
+      <x:c r="D17" s="9"/>
+      <x:c r="E17" s="9"/>
+      <x:c r="F17" s="9"/>
+      <x:c r="G17" s="10" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C16" s="13"/>
-      <x:c r="D16" s="13" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E16" s="13" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="F16" s="13" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="G16" s="13" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H16" s="13" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="I16" s="13" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="J16" s="13" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="K16" s="3"/>
-    </x:row>
-    <x:row r="17" spans="1:11">
-      <x:c r="A17" s="4"/>
-      <x:c r="B17" s="4"/>
-      <x:c r="C17" s="4"/>
-      <x:c r="D17" s="4"/>
-      <x:c r="E17" s="4"/>
-      <x:c r="F17" s="4"/>
-      <x:c r="G17" s="4"/>
-      <x:c r="H17" s="4"/>
-      <x:c r="I17" s="4"/>
-      <x:c r="J17" s="4"/>
-      <x:c r="K17" s="4"/>
-    </x:row>
-    <x:row r="18" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A18" s="8" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="B18" s="9"/>
-      <x:c r="C18" s="9"/>
-      <x:c r="D18" s="9"/>
-      <x:c r="E18" s="9"/>
-      <x:c r="F18" s="9"/>
-      <x:c r="G18" s="10" t="s">
-        <x:v>43</x:v>
-      </x:c>
+      <x:c r="H17" s="3"/>
+      <x:c r="I17" s="3"/>
+      <x:c r="J17" s="3"/>
+      <x:c r="K17" s="3"/>
+    </x:row>
+    <x:row r="18" spans="1:11">
+      <x:c r="A18" s="4"/>
+      <x:c r="B18" s="4"/>
+      <x:c r="C18" s="4"/>
+      <x:c r="D18" s="4"/>
+      <x:c r="E18" s="4"/>
+      <x:c r="F18" s="4"/>
+      <x:c r="G18" s="4"/>
       <x:c r="H18" s="3"/>
       <x:c r="I18" s="3"/>
       <x:c r="J18" s="3"/>
       <x:c r="K18" s="3"/>
     </x:row>
-    <x:row r="19" spans="1:11">
-      <x:c r="A19" s="4"/>
-      <x:c r="B19" s="4"/>
-      <x:c r="C19" s="4"/>
-      <x:c r="D19" s="4"/>
-      <x:c r="E19" s="4"/>
-      <x:c r="F19" s="4"/>
-      <x:c r="G19" s="4"/>
+    <x:row r="19" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A19" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B19" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C19" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D19" s="11" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E19" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F19" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G19" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
       <x:c r="H19" s="3"/>
       <x:c r="I19" s="3"/>
       <x:c r="J19" s="3"/>
       <x:c r="K19" s="3"/>
     </x:row>
-    <x:row r="20" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A20" s="11" t="s">
+    <x:row r="20" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A20" s="12" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B20" s="12" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C20" s="12" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="B20" s="11" t="s">
+      <x:c r="D20" s="12" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="C20" s="11" t="s">
+      <x:c r="E20" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="D20" s="11" t="s">
+      <x:c r="F20" s="12" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G20" s="12" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="E20" s="11" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="F20" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G20" s="11" t="s">
-        <x:v>17</x:v>
       </x:c>
       <x:c r="H20" s="3"/>
       <x:c r="I20" s="3"/>
       <x:c r="J20" s="3"/>
       <x:c r="K20" s="3"/>
     </x:row>
-    <x:row r="21" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A21" s="13" t="s">
+    <x:row r="21" spans="1:11">
+      <x:c r="A21" s="4"/>
+      <x:c r="B21" s="4"/>
+      <x:c r="C21" s="4"/>
+      <x:c r="D21" s="4"/>
+      <x:c r="E21" s="4"/>
+      <x:c r="F21" s="4"/>
+      <x:c r="G21" s="4"/>
+      <x:c r="H21" s="4"/>
+      <x:c r="I21" s="4"/>
+      <x:c r="J21" s="4"/>
+      <x:c r="K21" s="4"/>
+    </x:row>
+    <x:row r="22" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A22" s="8" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B22" s="9"/>
+      <x:c r="C22" s="9"/>
+      <x:c r="D22" s="9"/>
+      <x:c r="E22" s="9"/>
+      <x:c r="F22" s="9"/>
+      <x:c r="G22" s="9"/>
+      <x:c r="H22" s="9"/>
+      <x:c r="I22" s="9"/>
+      <x:c r="J22" s="9"/>
+      <x:c r="K22" s="10" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:11">
+      <x:c r="A23" s="4"/>
+      <x:c r="B23" s="4"/>
+      <x:c r="C23" s="4"/>
+      <x:c r="D23" s="4"/>
+      <x:c r="E23" s="4"/>
+      <x:c r="F23" s="4"/>
+      <x:c r="G23" s="4"/>
+      <x:c r="H23" s="4"/>
+      <x:c r="I23" s="4"/>
+      <x:c r="J23" s="4"/>
+      <x:c r="K23" s="4"/>
+    </x:row>
+    <x:row r="24" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A24" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B24" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C24" s="11" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="B21" s="13" t="s">
+      <x:c r="D24" s="11" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C21" s="13" t="s">
+      <x:c r="E24" s="11" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="D21" s="13" t="s">
+      <x:c r="F24" s="11" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E21" s="13" t="s">
+      <x:c r="G24" s="11" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="F21" s="13" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G21" s="13" t="s">
+      <x:c r="H24" s="11" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="H21" s="3"/>
-      <x:c r="I21" s="3"/>
-      <x:c r="J21" s="3"/>
-      <x:c r="K21" s="3"/>
-    </x:row>
-    <x:row r="22" spans="1:11">
-      <x:c r="A22" s="4"/>
-      <x:c r="B22" s="4"/>
-      <x:c r="C22" s="4"/>
-      <x:c r="D22" s="4"/>
-      <x:c r="E22" s="4"/>
-      <x:c r="F22" s="4"/>
-      <x:c r="G22" s="4"/>
-      <x:c r="H22" s="4"/>
-      <x:c r="I22" s="4"/>
-      <x:c r="J22" s="4"/>
-      <x:c r="K22" s="4"/>
-    </x:row>
-    <x:row r="23" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A23" s="8" t="s">
+      <x:c r="I24" s="11" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="B23" s="9"/>
-      <x:c r="C23" s="9"/>
-      <x:c r="D23" s="9"/>
-      <x:c r="E23" s="9"/>
-      <x:c r="F23" s="9"/>
-      <x:c r="G23" s="9"/>
-      <x:c r="H23" s="9"/>
-      <x:c r="I23" s="9"/>
-      <x:c r="J23" s="9"/>
-      <x:c r="K23" s="10" t="s">
+      <x:c r="J24" s="11" t="s">
         <x:v>56</x:v>
       </x:c>
-    </x:row>
-    <x:row r="24" spans="1:11">
-      <x:c r="A24" s="4"/>
-      <x:c r="B24" s="4"/>
-      <x:c r="C24" s="4"/>
-      <x:c r="D24" s="4"/>
-      <x:c r="E24" s="4"/>
-      <x:c r="F24" s="4"/>
-      <x:c r="G24" s="4"/>
-      <x:c r="H24" s="4"/>
-      <x:c r="I24" s="4"/>
-      <x:c r="J24" s="4"/>
-      <x:c r="K24" s="4"/>
-    </x:row>
-    <x:row r="25" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A25" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B25" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C25" s="11" t="s">
+      <x:c r="K24" s="11" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="D25" s="11" t="s">
+    </x:row>
+    <x:row r="25" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A25" s="12" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="E25" s="11" t="s">
+      <x:c r="B25" s="12" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="F25" s="11" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="G25" s="11" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="H25" s="11" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="I25" s="11" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="J25" s="11" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="K25" s="11" t="s">
-        <x:v>65</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A26" s="13" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="B26" s="13" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C26" s="13" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="D26" s="13" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="E26" s="13" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="F26" s="13" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="G26" s="13" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="H26" s="13" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I26" s="13" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="J26" s="13" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="K26" s="13" t="s">
-        <x:v>67</x:v>
+      <x:c r="C25" s="12" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D25" s="12" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E25" s="12" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="F25" s="12" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G25" s="12" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="H25" s="12" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I25" s="12" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="J25" s="12" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="K25" s="12" t="s">
+        <x:v>59</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1316,9 +1255,9 @@
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="A7:F7"/>
-    <x:mergeCell ref="A13:F13"/>
-    <x:mergeCell ref="A18:F18"/>
-    <x:mergeCell ref="A23:J23"/>
+    <x:mergeCell ref="A12:F12"/>
+    <x:mergeCell ref="A17:F17"/>
+    <x:mergeCell ref="A22:J22"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
